--- a/湖北农信新信贷数据库设计文档/新信贷_数据库设计_统一认证库-1.0.1.xlsx
+++ b/湖北农信新信贷数据库设计文档/新信贷_数据库设计_统一认证库-1.0.1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12540" firstSheet="6" activeTab="11"/>
+    <workbookView windowWidth="28800" windowHeight="12540" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="目录" sheetId="1" r:id="rId1"/>
@@ -231,7 +231,7 @@
     <t>idx_jrnl_LTST_DATA_IND_IDX</t>
   </si>
   <si>
-    <t>LTST_DATA_IND, FILE_SCM_TP, FILE_NM</t>
+    <t>LTST_DATA_IND,FILE_SCM_TP,FILE_NM</t>
   </si>
   <si>
     <t>btch_file_scm_un</t>
@@ -1669,6 +1669,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>varchar</t>
     </r>
     <r>
@@ -1683,6 +1688,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>varchar</t>
     </r>
     <r>
@@ -1715,6 +1725,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>varchar</t>
     </r>
     <r>
@@ -1922,6 +1937,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>varchar</t>
     </r>
     <r>
